--- a/Sermatec SMT-5K-TL-LV/Modbus-Register (HY-5K-TL-LV).xlsx
+++ b/Sermatec SMT-5K-TL-LV/Modbus-Register (HY-5K-TL-LV).xlsx
@@ -679,7 +679,7 @@
     <t xml:space="preserve">System Operating Mode (Werte noch unbekannt)</t>
   </si>
   <si>
-    <t xml:space="preserve">wurde nicht gesetzt</t>
+    <t xml:space="preserve">wurde weder gesetzt, noch abgefragt</t>
   </si>
   <si>
     <t xml:space="preserve">0x4053</t>
@@ -1638,9 +1638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>556200</xdr:colOff>
+      <xdr:colOff>557640</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>92520</xdr:rowOff>
+      <xdr:rowOff>92160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1650,7 +1650,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9669600" cy="17906040"/>
+          <a:ext cx="9669240" cy="17905680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1680,9 +1680,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>556200</xdr:colOff>
+      <xdr:colOff>557640</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>81720</xdr:rowOff>
+      <xdr:rowOff>81360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1692,7 +1692,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9669600" cy="11214000"/>
+          <a:ext cx="9669240" cy="11213640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1725,9 +1725,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>555840</xdr:colOff>
+      <xdr:colOff>557280</xdr:colOff>
       <xdr:row>97</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1737,7 +1737,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9669240" cy="20210760"/>
+          <a:ext cx="9668880" cy="20210400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1767,9 +1767,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>560520</xdr:colOff>
+      <xdr:colOff>561960</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>254160</xdr:rowOff>
+      <xdr:rowOff>253800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1779,7 +1779,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9673920" cy="18067680"/>
+          <a:ext cx="9673560" cy="18067320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4372,8 +4372,8 @@
       <c r="A88" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>59</v>
+      <c r="B88" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>60</v>
@@ -4456,8 +4456,8 @@
       <c r="A92" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>59</v>
+      <c r="B92" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>60</v>
@@ -4890,8 +4890,8 @@
       <c r="A108" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>59</v>
+      <c r="B108" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>60</v>
@@ -4920,8 +4920,8 @@
       <c r="A109" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>59</v>
+      <c r="B109" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>60</v>
@@ -4962,8 +4962,8 @@
       <c r="A111" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B111" s="7" t="s">
-        <v>59</v>
+      <c r="B111" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>60</v>
@@ -5034,8 +5034,8 @@
       <c r="A114" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B114" s="7" t="s">
-        <v>59</v>
+      <c r="B114" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>60</v>
